--- a/data/trans_dic/P21D_4_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,27</t>
+          <t>0,07; 1,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,69</t>
+          <t>0,16; 1,56</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,98</t>
+          <t>1,76; 6,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,76</t>
+          <t>1,26; 4,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,39</t>
+          <t>0,49; 4,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,13</t>
+          <t>0,24; 2,07</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,23</t>
+          <t>0,39; 3,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,5</t>
+          <t>0,19; 1,67</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,52</t>
+          <t>0,05; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,31</t>
+          <t>0,49; 1,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,76</t>
+          <t>0,31; 0,81</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 942</t>
+          <t>0; 833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 920</t>
+          <t>0; 872</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5976</t>
+          <t>0; 5227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163; 5353</t>
+          <t>164; 4518</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>751; 7562</t>
+          <t>698; 7001</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 4189</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2547; 10157</t>
+          <t>2564; 10175</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2833; 11440</t>
+          <t>3026; 11430</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6648</t>
+          <t>0; 6235</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7332</t>
+          <t>0; 6469</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1243</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>345; 3136</t>
+          <t>348; 3173</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>351; 3026</t>
+          <t>346; 2946</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1354</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1201</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1240; 9915</t>
+          <t>1189; 9620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1123; 9268</t>
+          <t>1170; 10331</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4549</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5161</t>
+          <t>0; 5438</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>676; 8695</t>
+          <t>796; 9442</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8255; 20783</t>
+          <t>7828; 21203</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9917; 24816</t>
+          <t>10170; 26447</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_4_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Provincia-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,91</t>
+          <t>0,23; 2,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,56</t>
+          <t>0,21; 1,69</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,99</t>
+          <t>1,67; 6,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,75</t>
+          <t>1,13; 4,56</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,45</t>
+          <t>0,47; 4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,07</t>
+          <t>0,23; 2,47</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,13</t>
+          <t>0,2; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,67</t>
+          <t>0,1; 1,47</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,57</t>
+          <t>0,07; 0,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,33</t>
+          <t>0,52; 1,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,81</t>
+          <t>0,36; 0,82</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>509</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>509</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 833</t>
+          <t>0; 2806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 872</t>
+          <t>0; 2494</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2921</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 4331</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164; 4518</t>
+          <t>582; 5524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>698; 7001</t>
+          <t>978; 8014</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4189</t>
+          <t>0; 2988</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2564; 10175</t>
+          <t>2438; 9972</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3026; 11430</t>
+          <t>2706; 10923</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 6638</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6469</t>
+          <t>0; 6738</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1258</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>348; 3173</t>
+          <t>372; 3412</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>346; 2946</t>
+          <t>373; 4045</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3757</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1189; 9620</t>
+          <t>710; 10028</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1170; 10331</t>
+          <t>729; 10394</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1458</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 5146</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 5282</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>17667</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>796; 9442</t>
+          <t>1149; 8584</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7828; 21203</t>
+          <t>8822; 21994</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10170; 26447</t>
+          <t>11739; 26607</t>
         </is>
       </c>
     </row>
